--- a/tables_and_figures/table5_jaccard_categories.xlsx
+++ b/tables_and_figures/table5_jaccard_categories.xlsx
@@ -458,7 +458,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Mental symptoms</t>
+          <t>Mental/cognitive symptoms</t>
         </is>
       </c>
       <c r="B4" t="n">
